--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,687 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129906015</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fridhem, Fridhem, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>501012</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6599316</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129896023</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fridhem, Fridhem, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>501058</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6599320</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129903755</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500959</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6600190</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Charlotte Lemte</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Charlotte Lemte</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129895972</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fridhem, Fridhem, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500995</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6599388</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Camilla Berglund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Camilla Berglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129896576</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lönntorpet, Lönntorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500951</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6599774</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129905865</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lönntorpet, Lönntorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500904</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6599803</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Camilla Berglund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Camilla Berglund, Mattias Drejby, Lisbet Olsen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1472,6 +1472,945 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129912712</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92919</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>501017</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6599371</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>gammal fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129912710</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>500985</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6599393</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>gammalt spår  gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129912709</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>500964</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6599283</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födosök myrstack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129912695</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>500971</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6599949</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129912703</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>500952</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6599598</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129912698</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92919</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>500999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6599488</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>gammal fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129912704</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>501025</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6599327</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129912714</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>501011</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6599258</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129912700</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97660</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>500917</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6599887</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129912710</v>
+        <v>129912698</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>92919</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500985</v>
+        <v>500999</v>
       </c>
       <c r="R10" t="n">
-        <v>6599393</v>
+        <v>6599488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>gammalt spår  gran</t>
+          <t>gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129912709</v>
+        <v>129912700</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>97664</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,26 +1697,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102977</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500964</v>
+        <v>500917</v>
       </c>
       <c r="R11" t="n">
-        <v>6599283</v>
+        <v>6599887</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,11 +1761,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosök myrstack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,7 +1787,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129912695</v>
+        <v>129912710</v>
       </c>
       <c r="B12" t="n">
         <v>57733</v>
@@ -1825,16 +1820,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500971</v>
+        <v>500985</v>
       </c>
       <c r="R12" t="n">
-        <v>6599949</v>
+        <v>6599393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,7 +1874,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>spår i torraka</t>
+          <t>gammalt spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,6 +1885,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1898,27 +1916,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129912703</v>
+        <v>129896024</v>
       </c>
       <c r="B13" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1926,24 +1944,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500952</v>
+        <v>500963</v>
       </c>
       <c r="R13" t="n">
-        <v>6599598</v>
+        <v>6599553</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1970,11 +1989,26 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1983,26 +2017,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129912698</v>
+        <v>129895869</v>
       </c>
       <c r="B14" t="n">
-        <v>92919</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2010,41 +2069,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Lugnet, Nora, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500999</v>
+        <v>500985</v>
       </c>
       <c r="R14" t="n">
-        <v>6599488</v>
+        <v>6599289</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,14 +2131,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>gammal fruktkropp</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,26 +2154,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129912704</v>
+        <v>129912709</v>
       </c>
       <c r="B15" t="n">
-        <v>58106</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2138,16 +2208,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501025</v>
+        <v>500964</v>
       </c>
       <c r="R15" t="n">
-        <v>6599327</v>
+        <v>6599283</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,6 +2258,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosök myrstack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,27 +2289,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129912714</v>
+        <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2234,24 +2317,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501011</v>
+        <v>500886</v>
       </c>
       <c r="R16" t="n">
-        <v>6599258</v>
+        <v>6600282</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2278,14 +2362,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2296,65 +2385,78 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129912700</v>
+        <v>129912695</v>
       </c>
       <c r="B17" t="n">
-        <v>97660</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500917</v>
+        <v>500971</v>
       </c>
       <c r="R17" t="n">
-        <v>6599887</v>
+        <v>6599949</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,6 +2491,11 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2410,6 +2517,455 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129912703</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>500952</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6599598</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129912704</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>501025</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6599327</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129896090</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stadsskogen, Nora sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>500999</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6599755</v>
+      </c>
+      <c r="S20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129912714</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>501011</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6599258</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mattias Drejby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B20" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,25 +2766,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R20" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2811,19 +2818,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,48 +2836,43 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2883,32 +2880,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R21" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2935,14 +2925,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,16 +2948,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>129906015</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129896023</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>129903755</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129895972</v>
       </c>
       <c r="B6" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129896576</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129905865</v>
       </c>
       <c r="B8" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129912712</v>
       </c>
       <c r="B9" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129912698</v>
       </c>
       <c r="B10" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129912700</v>
       </c>
       <c r="B11" t="n">
-        <v>97664</v>
+        <v>97668</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129912710</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129896024</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>129895869</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129912709</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2289,27 +2289,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129896455</v>
+        <v>129912695</v>
       </c>
       <c r="B16" t="n">
-        <v>58106</v>
+        <v>57734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2317,25 +2317,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500886</v>
+        <v>500971</v>
       </c>
       <c r="R16" t="n">
-        <v>6600282</v>
+        <v>6599949</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2362,19 +2369,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,48 +2387,43 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129912695</v>
+        <v>129896455</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>58108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2434,32 +2431,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500971</v>
+        <v>500886</v>
       </c>
       <c r="R17" t="n">
-        <v>6599949</v>
+        <v>6600282</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,14 +2476,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>spår i torraka</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,16 +2499,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>58108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,32 +2766,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R20" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2818,14 +2811,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,43 +2834,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>58106</v>
+        <v>57734</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2880,25 +2883,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R21" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,19 +2935,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,21 +2953,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129906015</v>
+        <v>129896023</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,42 +804,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501012</v>
+        <v>501058</v>
       </c>
       <c r="R3" t="n">
-        <v>6599316</v>
+        <v>6599320</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129896023</v>
+        <v>129906015</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,37 +911,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501058</v>
+        <v>501012</v>
       </c>
       <c r="R4" t="n">
-        <v>6599320</v>
+        <v>6599316</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2289,27 +2289,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129912695</v>
+        <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>57734</v>
+        <v>58108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2317,32 +2317,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500971</v>
+        <v>500886</v>
       </c>
       <c r="R16" t="n">
-        <v>6599949</v>
+        <v>6600282</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,14 +2362,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>spår i torraka</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,43 +2385,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129896455</v>
+        <v>129912695</v>
       </c>
       <c r="B17" t="n">
-        <v>58108</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,25 +2434,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500886</v>
+        <v>500971</v>
       </c>
       <c r="R17" t="n">
-        <v>6600282</v>
+        <v>6599949</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2476,19 +2486,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,21 +2504,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B20" t="n">
-        <v>58108</v>
+        <v>57734</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,25 +2766,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R20" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2811,19 +2818,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,48 +2836,43 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B21" t="n">
-        <v>57734</v>
+        <v>58108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2883,32 +2880,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R21" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2935,14 +2925,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,16 +2948,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2058,53 +2058,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129895869</v>
+        <v>129912709</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Nora, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500985</v>
+        <v>500964</v>
       </c>
       <c r="R14" t="n">
-        <v>6599289</v>
+        <v>6599283</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,19 +2138,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosök myrstack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,81 +2156,69 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129912709</v>
+        <v>129895869</v>
       </c>
       <c r="B15" t="n">
-        <v>57731</v>
+        <v>57895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Lugnet, Nora, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500964</v>
+        <v>500985</v>
       </c>
       <c r="R15" t="n">
-        <v>6599283</v>
+        <v>6599289</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,14 +2245,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök myrstack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,43 +2268,48 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129896455</v>
+        <v>129912695</v>
       </c>
       <c r="B16" t="n">
-        <v>58108</v>
+        <v>57734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2317,25 +2317,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500886</v>
+        <v>500971</v>
       </c>
       <c r="R16" t="n">
-        <v>6600282</v>
+        <v>6599949</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2362,19 +2369,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,48 +2387,43 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129912695</v>
+        <v>129896455</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>58108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2434,32 +2431,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500971</v>
+        <v>500886</v>
       </c>
       <c r="R17" t="n">
-        <v>6599949</v>
+        <v>6600282</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,14 +2476,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>spår i torraka</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,16 +2499,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>57734</v>
+        <v>58108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,32 +2766,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R20" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2818,14 +2811,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,43 +2834,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>58108</v>
+        <v>57734</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2880,25 +2883,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R21" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,19 +2935,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,21 +2953,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129896023</v>
+        <v>129906015</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,37 +804,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501058</v>
+        <v>501012</v>
       </c>
       <c r="R3" t="n">
-        <v>6599320</v>
+        <v>6599316</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129906015</v>
+        <v>129896023</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,42 +916,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501012</v>
+        <v>501058</v>
       </c>
       <c r="R4" t="n">
-        <v>6599316</v>
+        <v>6599320</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
         <v>129903755</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129895972</v>
       </c>
       <c r="B6" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129896576</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129905865</v>
       </c>
       <c r="B8" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129912712</v>
       </c>
       <c r="B9" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129912698</v>
       </c>
       <c r="B10" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129912700</v>
       </c>
       <c r="B11" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129912710</v>
       </c>
       <c r="B12" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129896024</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,60 +2058,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129912709</v>
+        <v>129895869</v>
       </c>
       <c r="B14" t="n">
-        <v>57731</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Lugnet, Nora, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500964</v>
+        <v>500985</v>
       </c>
       <c r="R14" t="n">
-        <v>6599283</v>
+        <v>6599289</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,14 +2131,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosök myrstack</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,69 +2154,81 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129895869</v>
+        <v>129912709</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Nora, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500985</v>
+        <v>500964</v>
       </c>
       <c r="R15" t="n">
-        <v>6599289</v>
+        <v>6599283</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2245,19 +2255,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosök myrstack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,21 +2273,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
         <v>129912695</v>
       </c>
       <c r="B16" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>129896455</v>
       </c>
       <c r="B17" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B20" t="n">
-        <v>58108</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,25 +2766,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R20" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2811,19 +2818,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,48 +2836,43 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B21" t="n">
-        <v>57734</v>
+        <v>58111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2883,32 +2880,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R21" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2935,14 +2925,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,16 +2948,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>58111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,32 +2766,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R20" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2818,14 +2811,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,43 +2834,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>58111</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2880,25 +2883,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R21" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,19 +2935,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,21 +2953,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>129896023</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>129903755</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129895972</v>
       </c>
       <c r="B6" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129896576</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129905865</v>
       </c>
       <c r="B8" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129912712</v>
       </c>
       <c r="B9" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129912698</v>
       </c>
       <c r="B10" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129912700</v>
       </c>
       <c r="B11" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2289,27 +2289,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129912695</v>
+        <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>58111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2317,32 +2317,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500971</v>
+        <v>500886</v>
       </c>
       <c r="R16" t="n">
-        <v>6599949</v>
+        <v>6600282</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,14 +2362,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>spår i torraka</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,43 +2385,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129896455</v>
+        <v>129912695</v>
       </c>
       <c r="B17" t="n">
-        <v>58111</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,25 +2434,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500886</v>
+        <v>500971</v>
       </c>
       <c r="R17" t="n">
-        <v>6600282</v>
+        <v>6599949</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2476,19 +2486,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,21 +2504,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B20" t="n">
-        <v>58111</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,25 +2766,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R20" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2811,19 +2818,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,48 +2836,43 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>58111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2883,32 +2880,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R21" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2935,14 +2925,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,16 +2948,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129906015</v>
+        <v>129896023</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,42 +804,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501012</v>
+        <v>501058</v>
       </c>
       <c r="R3" t="n">
-        <v>6599316</v>
+        <v>6599320</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129896023</v>
+        <v>129906015</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,37 +911,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501058</v>
+        <v>501012</v>
       </c>
       <c r="R4" t="n">
-        <v>6599320</v>
+        <v>6599316</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
         <v>129903755</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129895972</v>
       </c>
       <c r="B6" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129896576</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129905865</v>
       </c>
       <c r="B8" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129912712</v>
       </c>
       <c r="B9" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129912698</v>
       </c>
       <c r="B10" t="n">
-        <v>92926</v>
+        <v>92943</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129912700</v>
       </c>
       <c r="B11" t="n">
-        <v>97672</v>
+        <v>97689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2058,53 +2058,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129895869</v>
+        <v>129912709</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Nora, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500985</v>
+        <v>500964</v>
       </c>
       <c r="R14" t="n">
-        <v>6599289</v>
+        <v>6599283</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,19 +2138,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosök myrstack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,81 +2156,69 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129912709</v>
+        <v>129895869</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Lugnet, Nora, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500964</v>
+        <v>500985</v>
       </c>
       <c r="R15" t="n">
-        <v>6599283</v>
+        <v>6599289</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,14 +2245,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök myrstack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,16 +2268,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
         <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>58112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,32 +2766,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R20" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2818,14 +2811,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,43 +2834,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>58111</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2880,25 +2883,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R21" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,19 +2935,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,21 +2953,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129896023</v>
+        <v>129906015</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,37 +804,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501058</v>
+        <v>501012</v>
       </c>
       <c r="R3" t="n">
-        <v>6599320</v>
+        <v>6599316</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129906015</v>
+        <v>129896023</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,42 +916,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501012</v>
+        <v>501058</v>
       </c>
       <c r="R4" t="n">
-        <v>6599316</v>
+        <v>6599320</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>129895972</v>
       </c>
       <c r="B6" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129905865</v>
       </c>
       <c r="B8" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129912712</v>
       </c>
       <c r="B9" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129912698</v>
       </c>
       <c r="B10" t="n">
-        <v>92959</v>
+        <v>92961</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129912700</v>
       </c>
       <c r="B11" t="n">
-        <v>97705</v>
+        <v>97707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2289,27 +2289,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129896455</v>
+        <v>129912695</v>
       </c>
       <c r="B16" t="n">
-        <v>58113</v>
+        <v>57738</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2317,25 +2317,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500886</v>
+        <v>500971</v>
       </c>
       <c r="R16" t="n">
-        <v>6600282</v>
+        <v>6599949</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2362,19 +2369,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,48 +2387,43 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129912695</v>
+        <v>129896455</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>58113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2434,32 +2431,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500971</v>
+        <v>500886</v>
       </c>
       <c r="R17" t="n">
-        <v>6599949</v>
+        <v>6600282</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,14 +2476,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>spår i torraka</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,16 +2499,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129906015</v>
+        <v>129896023</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,42 +804,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501012</v>
+        <v>501058</v>
       </c>
       <c r="R3" t="n">
-        <v>6599316</v>
+        <v>6599320</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129896023</v>
+        <v>129906015</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,37 +911,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501058</v>
+        <v>501012</v>
       </c>
       <c r="R4" t="n">
-        <v>6599320</v>
+        <v>6599316</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
         <v>129903755</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129895972</v>
       </c>
       <c r="B6" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129896576</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129905865</v>
       </c>
       <c r="B8" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129912712</v>
       </c>
       <c r="B9" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129912698</v>
       </c>
       <c r="B10" t="n">
-        <v>92961</v>
+        <v>93048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129912700</v>
       </c>
       <c r="B11" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129912710</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129896024</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>129895869</v>
       </c>
       <c r="B14" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>129912709</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2289,27 +2289,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129912695</v>
+        <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>58198</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2317,32 +2317,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500971</v>
+        <v>500886</v>
       </c>
       <c r="R16" t="n">
-        <v>6599949</v>
+        <v>6600282</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,14 +2362,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>spår i torraka</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,43 +2385,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129896455</v>
+        <v>129912695</v>
       </c>
       <c r="B17" t="n">
-        <v>58113</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2431,25 +2434,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500886</v>
+        <v>500971</v>
       </c>
       <c r="R17" t="n">
-        <v>6600282</v>
+        <v>6599949</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2476,19 +2486,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,21 +2504,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B20" t="n">
-        <v>58198</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,25 +2766,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R20" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2811,19 +2818,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,48 +2836,43 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>58198</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2883,32 +2880,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R21" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2935,14 +2925,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,16 +2948,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2738,27 +2738,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129912714</v>
+        <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>58198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2766,32 +2766,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501011</v>
+        <v>500999</v>
       </c>
       <c r="R20" t="n">
-        <v>6599258</v>
+        <v>6599755</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2818,14 +2811,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,43 +2834,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129896090</v>
+        <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>58198</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2880,25 +2883,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500999</v>
+        <v>501011</v>
       </c>
       <c r="R21" t="n">
-        <v>6599755</v>
+        <v>6599258</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,19 +2935,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:44</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,21 +2953,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2058,53 +2058,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129895869</v>
+        <v>129912709</v>
       </c>
       <c r="B14" t="n">
-        <v>57985</v>
+        <v>57820</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lugnet, Nora, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500985</v>
+        <v>500964</v>
       </c>
       <c r="R14" t="n">
-        <v>6599289</v>
+        <v>6599283</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2131,19 +2138,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosök myrstack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,81 +2156,69 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129912709</v>
+        <v>129895869</v>
       </c>
       <c r="B15" t="n">
-        <v>57820</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Lugnet, Nora, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500964</v>
+        <v>500985</v>
       </c>
       <c r="R15" t="n">
-        <v>6599283</v>
+        <v>6599289</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,14 +2245,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Födosök myrstack</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,16 +2268,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129896023</v>
+        <v>129906015</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,37 +804,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501058</v>
+        <v>501012</v>
       </c>
       <c r="R3" t="n">
-        <v>6599320</v>
+        <v>6599316</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129906015</v>
+        <v>129896023</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,42 +916,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501012</v>
+        <v>501058</v>
       </c>
       <c r="R4" t="n">
-        <v>6599316</v>
+        <v>6599320</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
         <v>129903755</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129895972</v>
       </c>
       <c r="B6" t="n">
-        <v>93010</v>
+        <v>92923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>129896576</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129905865</v>
       </c>
       <c r="B8" t="n">
-        <v>93010</v>
+        <v>92923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>129912712</v>
       </c>
       <c r="B9" t="n">
-        <v>93048</v>
+        <v>92961</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>129912698</v>
       </c>
       <c r="B10" t="n">
-        <v>93048</v>
+        <v>92961</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>129912700</v>
       </c>
       <c r="B11" t="n">
-        <v>97794</v>
+        <v>97707</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129912710</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129896024</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2058,60 +2058,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129912709</v>
+        <v>129895869</v>
       </c>
       <c r="B14" t="n">
-        <v>57820</v>
+        <v>57900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Lugnet, Nora, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500964</v>
+        <v>500985</v>
       </c>
       <c r="R14" t="n">
-        <v>6599283</v>
+        <v>6599289</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,14 +2131,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosök myrstack</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,69 +2154,81 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129895869</v>
+        <v>129912709</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Nora, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500985</v>
+        <v>500964</v>
       </c>
       <c r="R15" t="n">
-        <v>6599289</v>
+        <v>6599283</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2245,19 +2255,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosök myrstack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,48 +2273,43 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129896455</v>
+        <v>129912695</v>
       </c>
       <c r="B16" t="n">
-        <v>58198</v>
+        <v>57738</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2317,25 +2317,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500886</v>
+        <v>500971</v>
       </c>
       <c r="R16" t="n">
-        <v>6600282</v>
+        <v>6599949</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2362,19 +2369,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,48 +2387,43 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129912695</v>
+        <v>129896455</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>58113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2434,32 +2431,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500971</v>
+        <v>500886</v>
       </c>
       <c r="R17" t="n">
-        <v>6599949</v>
+        <v>6600282</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,14 +2476,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>spår i torraka</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,16 +2499,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58198</v>
+        <v>58113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58198</v>
+        <v>58113</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>58198</v>
+        <v>58113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -2292,7 +2292,7 @@
         <v>129896455</v>
       </c>
       <c r="B16" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129896090</v>
       </c>
       <c r="B20" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>129906015</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129912710</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129896024</v>
       </c>
       <c r="B13" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>129912709</v>
       </c>
       <c r="B14" t="n">
-        <v>57878</v>
+        <v>57880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>129895869</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>129912695</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>129906015</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129912710</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129896024</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>129912709</v>
       </c>
       <c r="B14" t="n">
-        <v>57880</v>
+        <v>57881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>129895869</v>
       </c>
       <c r="B15" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>129912695</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129912714</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>129896576</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>129896576</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -675,54 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97611730</v>
+        <v>129895972</v>
       </c>
       <c r="B2" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nora, Vstm</t>
+          <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500945.7711584172</v>
+        <v>500995</v>
       </c>
       <c r="R2" t="n">
-        <v>6599941.339838368</v>
+        <v>6599388</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,27 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vid granbas</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,28 +775,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johanna Arvidsson</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Arvidsson</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129906015</v>
+        <v>129905865</v>
       </c>
       <c r="B3" t="n">
-        <v>57889</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,42 +810,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fridhem, Fridhem, Vstm</t>
+          <t>Lönntorpet, Lönntorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501012</v>
+        <v>500904</v>
       </c>
       <c r="R3" t="n">
-        <v>6599316</v>
+        <v>6599803</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,66 +899,73 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Camilla Berglund, Mattias Drejby, Lisbet Olsen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129896023</v>
+        <v>97611730</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fridhem, Fridhem, Vstm</t>
+          <t>Nora, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501058</v>
+        <v>500945</v>
       </c>
       <c r="R4" t="n">
-        <v>6599320</v>
+        <v>6599942</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,22 +989,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:33</t>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vid granbas</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Johanna Arvidsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Johanna Arvidsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129903755</v>
+        <v>129912698</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,37 +1037,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500959</v>
+        <v>500999</v>
       </c>
       <c r="R5" t="n">
-        <v>6600190</v>
+        <v>6599488</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,19 +1098,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:09</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,71 +1120,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Charlotte Lemte</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Charlotte Lemte</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129895972</v>
+        <v>129912712</v>
       </c>
       <c r="B6" t="n">
-        <v>93010</v>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fridhem, Fridhem, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500995</v>
+        <v>501017</v>
       </c>
       <c r="R6" t="n">
-        <v>6599388</v>
+        <v>6599371</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,19 +1204,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,38 +1220,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Camilla Berglund</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Camilla Berglund</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129896576</v>
+        <v>129896023</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1274,17 +1269,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lönntorpet, Lönntorpet, Vstm</t>
+          <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500951</v>
+        <v>501058</v>
       </c>
       <c r="R7" t="n">
-        <v>6599774</v>
+        <v>6599320</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129905865</v>
+        <v>129896024</v>
       </c>
       <c r="B8" t="n">
-        <v>93010</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,48 +1356,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lönntorpet, Lönntorpet, Vstm</t>
+          <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500904</v>
+        <v>500963</v>
       </c>
       <c r="R8" t="n">
-        <v>6599803</v>
+        <v>6599553</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1430,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,76 +1444,96 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Camilla Berglund</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Camilla Berglund, Mattias Drejby, Lisbet Olsen</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129912712</v>
+        <v>129901742</v>
       </c>
       <c r="B9" t="n">
-        <v>93048</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501017</v>
+        <v>500983</v>
       </c>
       <c r="R9" t="n">
-        <v>6599371</v>
+        <v>6599860</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,14 +1560,24 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>gammal fruktkropp</t>
+          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,68 +1588,94 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129912698</v>
+        <v>129906015</v>
       </c>
       <c r="B10" t="n">
-        <v>93048</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Fridhem, Fridhem, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500999</v>
+        <v>501012</v>
       </c>
       <c r="R10" t="n">
-        <v>6599488</v>
+        <v>6599316</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,14 +1702,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>gammal fruktkropp</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,22 +1729,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129912700</v>
+        <v>129912695</v>
       </c>
       <c r="B11" t="n">
-        <v>97794</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,38 +1752,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500917</v>
+        <v>500971</v>
       </c>
       <c r="R11" t="n">
-        <v>6599887</v>
+        <v>6599949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,6 +1824,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>spår i torraka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,11 +1858,11 @@
         <v>129912710</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1916,14 +1984,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129896024</v>
+        <v>129912711</v>
       </c>
       <c r="B13" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1944,25 +2012,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fridhem, Fridhem, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500963</v>
+        <v>500989</v>
       </c>
       <c r="R13" t="n">
-        <v>6599553</v>
+        <v>6599852</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,24 +2064,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska hack i död tall</t>
+          <t>gammalt spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,50 +2083,40 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129912709</v>
+        <v>129912714</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,21 +2124,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2095,7 +2150,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2105,10 +2160,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500964</v>
+        <v>501011</v>
       </c>
       <c r="R14" t="n">
-        <v>6599283</v>
+        <v>6599258</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2200,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosök myrstack</t>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,53 +2227,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129895869</v>
+        <v>129912709</v>
       </c>
       <c r="B15" t="n">
-        <v>58050</v>
+        <v>57947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnet, Nora, Nora sn, Vstm</t>
+          <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500985</v>
+        <v>500964</v>
       </c>
       <c r="R15" t="n">
-        <v>6599289</v>
+        <v>6599283</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2245,19 +2307,14 @@
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosök myrstack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,31 +2325,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129896455</v>
+        <v>129896090</v>
       </c>
       <c r="B16" t="n">
-        <v>58256</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,14 +2377,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vargaflyet, Vargaflyet, Vstm</t>
+          <t>Stadsskogen, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500886</v>
+        <v>500999</v>
       </c>
       <c r="R16" t="n">
-        <v>6600282</v>
+        <v>6599755</v>
       </c>
       <c r="S16" t="n">
         <v>30</v>
@@ -2364,7 +2416,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,7 +2426,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,27 +2458,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129912695</v>
+        <v>129896455</v>
       </c>
       <c r="B17" t="n">
-        <v>57889</v>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2434,32 +2486,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stadskogen, Nora, Vstm, Vstm</t>
+          <t>Vargaflyet, Vargaflyet, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500971</v>
+        <v>500886</v>
       </c>
       <c r="R17" t="n">
-        <v>6599949</v>
+        <v>6600282</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,14 +2531,19 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>spår i torraka</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,16 +2554,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2523,7 +2578,7 @@
         <v>129912703</v>
       </c>
       <c r="B18" t="n">
-        <v>58256</v>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2687,7 @@
         <v>129912704</v>
       </c>
       <c r="B19" t="n">
-        <v>58256</v>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,32 +2793,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129896090</v>
+        <v>129895869</v>
       </c>
       <c r="B20" t="n">
-        <v>58256</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2774,17 +2829,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stadsskogen, Nora sn, Vstm</t>
+          <t>Lugnet, Nora, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500999</v>
+        <v>500985</v>
       </c>
       <c r="R20" t="n">
-        <v>6599755</v>
+        <v>6599289</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2868,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2878,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,57 +2910,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129912714</v>
+        <v>129912700</v>
       </c>
       <c r="B21" t="n">
-        <v>57889</v>
+        <v>97986</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stadskogen, Nora, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>501011</v>
+        <v>500917</v>
       </c>
       <c r="R21" t="n">
-        <v>6599258</v>
+        <v>6599887</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,11 +2985,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 57511-2025 artfynd.xlsx
+++ b/artfynd/A 57511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129895972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129905865</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97611730</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912698</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912712</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129896023</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129896024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1626,6 +1666,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129901742</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1738,6 +1783,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129906015</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1852,6 +1902,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912695</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1981,6 +2036,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912710</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2110,6 +2170,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912711</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2224,6 +2289,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912714</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2338,6 +2408,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912709</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2455,6 +2530,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129896090</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2572,6 +2652,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129896455</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2681,6 +2766,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912703</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2790,6 +2880,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912704</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2907,6 +3002,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129895869</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3008,8 +3108,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129912700</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>